--- a/public/templates/import-kategori-ekstrakurikuler.xlsx
+++ b/public/templates/import-kategori-ekstrakurikuler.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ekskulio\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98C0FE6-6BBF-43D8-80DC-8ECB51A024F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E27484B-03E1-4DC6-B4CC-596627FF7349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1008" windowWidth="21600" windowHeight="11232" xr2:uid="{CDC1ACF0-9087-4BBD-A3C1-E4B7A3B0C523}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CDC1ACF0-9087-4BBD-A3C1-E4B7A3B0C523}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>nama_kategori</t>
   </si>
@@ -89,6 +89,41 @@
         <scheme val="minor"/>
       </rPr>
       <t>hanya opsional.</t>
+    </r>
+  </si>
+  <si>
+    <t>kode_kategori</t>
+  </si>
+  <si>
+    <t>OBD</t>
+  </si>
+  <si>
+    <t>SDB</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kode_kategori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bersifat opsional. Jika kosong, maka akan di-generate oleh sistem.</t>
     </r>
   </si>
 </sst>
@@ -121,7 +156,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -129,16 +164,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -456,44 +512,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865C1D33-BA53-4B78-BF39-5FAA9EC9879E}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.21875" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -501,7 +591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -509,7 +599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -517,7 +607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -525,7 +615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -534,6 +624,11 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E3:L3"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E1:L1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>